--- a/DesignerConfigs/Datas/__tables__.xlsx
+++ b/DesignerConfigs/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>MoneyInterval.xlsx</t>
+  </si>
+  <si>
+    <t>TBOrderStateInfo</t>
+  </si>
+  <si>
+    <t>ConfOrderStateInfo</t>
+  </si>
+  <si>
+    <t>OrderStateInfo.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1166,7 +1175,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="13.5" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9.83333333333333" customWidth="1"/>
@@ -1462,6 +1471,23 @@
         <v>34</v>
       </c>
     </row>
+    <row r="15" spans="1:13">
+      <c r="B15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
